--- a/pa-temp-fix-system.com/php/export/2006个SGU需要帮忙导入中文分类.xlsx
+++ b/pa-temp-fix-system.com/php/export/2006个SGU需要帮忙导入中文分类.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17970"/>
+    <workbookView windowWidth="31770" windowHeight="17970"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
